--- a/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (5)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (7)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBEE837-B524-4A06-8A95-EEF67843B54D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE37DB0-A964-4500-9B1B-D15472675205}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="50">
   <si>
     <t>备注</t>
   </si>
@@ -177,6 +177,12 @@
   </si>
   <si>
     <t>FE归还信息备注</t>
+  </si>
+  <si>
+    <t>备件号</t>
+  </si>
+  <si>
+    <t>备件描述</t>
   </si>
 </sst>
 </file>
@@ -815,64 +821,88 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.109375" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="25.88671875" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" customWidth="1"/>
-    <col min="7" max="7" width="22.88671875" customWidth="1"/>
-    <col min="8" max="9" width="17.6640625" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" customWidth="1"/>
-    <col min="11" max="11" width="18.88671875" customWidth="1"/>
-    <col min="12" max="12" width="19.44140625" customWidth="1"/>
-    <col min="13" max="13" width="19.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" customWidth="1"/>
+    <col min="7" max="7" width="30.109375" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" customWidth="1"/>
+    <col min="10" max="10" width="25.88671875" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.44140625" customWidth="1"/>
+    <col min="13" max="13" width="22.88671875" customWidth="1"/>
+    <col min="14" max="15" width="17.6640625" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" customWidth="1"/>
+    <col min="17" max="17" width="18.88671875" customWidth="1"/>
+    <col min="18" max="18" width="19.44140625" customWidth="1"/>
+    <col min="19" max="19" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.6">
+    <row r="1" spans="1:20" ht="15.6">
       <c r="A1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>45</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (7)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE37DB0-A964-4500-9B1B-D15472675205}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4411F4-3473-454D-BC2C-336AF5FC22D2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -98,9 +98,6 @@
     <t>运单号</t>
   </si>
   <si>
-    <t>归还日期</t>
-  </si>
-  <si>
     <t>新探头SN编号</t>
   </si>
   <si>
@@ -183,6 +180,9 @@
   </si>
   <si>
     <t>备件描述</t>
+  </si>
+  <si>
+    <t>归还时间</t>
   </si>
 </sst>
 </file>
@@ -600,58 +600,58 @@
   <sheetData>
     <row r="1" spans="1:21" s="4" customFormat="1" ht="15.6">
       <c r="A1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>13</v>
@@ -660,7 +660,7 @@
         <v>14</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -711,13 +711,13 @@
   <sheetData>
     <row r="1" spans="1:34" ht="15.6">
       <c r="A1" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>7</v>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
       <c r="I1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J1" t="s">
         <v>12</v>
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="L1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M1" t="s">
         <v>16</v>
@@ -756,19 +756,19 @@
         <v>18</v>
       </c>
       <c r="P1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q1" t="s">
         <v>3</v>
       </c>
       <c r="R1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S1" t="s">
         <v>34</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>35</v>
-      </c>
-      <c r="T1" t="s">
-        <v>36</v>
       </c>
       <c r="U1" t="s">
         <v>1</v>
@@ -777,19 +777,19 @@
         <v>2</v>
       </c>
       <c r="W1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X1" t="s">
         <v>42</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z1" t="s">
         <v>43</v>
       </c>
-      <c r="Y1" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>44</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>45</v>
       </c>
       <c r="AB1" t="s">
         <v>19</v>
@@ -804,13 +804,13 @@
         <v>20</v>
       </c>
       <c r="AF1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG1" t="s">
         <v>21</v>
       </c>
-      <c r="AG1" t="s">
-        <v>22</v>
-      </c>
       <c r="AH1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -846,10 +846,10 @@
   <sheetData>
     <row r="1" spans="1:20" ht="15.6">
       <c r="A1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>3</v>
@@ -864,19 +864,19 @@
         <v>0</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>8</v>
@@ -888,22 +888,22 @@
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="R1" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="S1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="T1" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (7)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4411F4-3473-454D-BC2C-336AF5FC22D2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61961D1-3788-47B0-9D17-89DAECA97F5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -182,7 +182,7 @@
     <t>备件描述</t>
   </si>
   <si>
-    <t>归还时间</t>
+    <t>归还日期</t>
   </si>
 </sst>
 </file>

--- a/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (7)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (4)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61961D1-3788-47B0-9D17-89DAECA97F5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A38543-519E-4CE6-A04E-4186142C4D71}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="人工申请" sheetId="1" r:id="rId1"/>
     <sheet name="探头申请" sheetId="2" r:id="rId2"/>
     <sheet name="备件申请" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="54">
   <si>
     <t>备注</t>
   </si>
@@ -183,6 +183,18 @@
   </si>
   <si>
     <t>归还日期</t>
+  </si>
+  <si>
+    <t>租户</t>
+  </si>
+  <si>
+    <t>合同号</t>
+  </si>
+  <si>
+    <t>区域</t>
+  </si>
+  <si>
+    <t>合同类型</t>
   </si>
 </sst>
 </file>
@@ -572,94 +584,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.21875" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" customWidth="1"/>
-    <col min="6" max="6" width="22.5546875" customWidth="1"/>
-    <col min="7" max="7" width="21.6640625" customWidth="1"/>
-    <col min="8" max="8" width="17.77734375" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" customWidth="1"/>
-    <col min="10" max="10" width="16.21875" customWidth="1"/>
-    <col min="11" max="11" width="21.44140625" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="23.5546875" customWidth="1"/>
-    <col min="15" max="15" width="20.5546875" customWidth="1"/>
-    <col min="16" max="16" width="14.88671875" customWidth="1"/>
-    <col min="17" max="17" width="17.5546875" customWidth="1"/>
-    <col min="18" max="18" width="18.6640625" customWidth="1"/>
-    <col min="19" max="19" width="23.88671875" customWidth="1"/>
-    <col min="20" max="20" width="22.6640625" customWidth="1"/>
-    <col min="21" max="21" width="16.88671875" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="24.21875" customWidth="1"/>
+    <col min="5" max="5" width="23.44140625" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="10" max="10" width="22.5546875" customWidth="1"/>
+    <col min="11" max="11" width="21.6640625" customWidth="1"/>
+    <col min="12" max="12" width="17.77734375" customWidth="1"/>
+    <col min="13" max="13" width="13.88671875" customWidth="1"/>
+    <col min="14" max="14" width="16.21875" customWidth="1"/>
+    <col min="15" max="15" width="21.44140625" customWidth="1"/>
+    <col min="16" max="16" width="18.77734375" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="23.5546875" customWidth="1"/>
+    <col min="19" max="19" width="20.5546875" customWidth="1"/>
+    <col min="20" max="20" width="14.88671875" customWidth="1"/>
+    <col min="21" max="21" width="17.5546875" customWidth="1"/>
+    <col min="22" max="22" width="18.6640625" customWidth="1"/>
+    <col min="23" max="23" width="23.88671875" customWidth="1"/>
+    <col min="24" max="24" width="22.6640625" customWidth="1"/>
+    <col min="25" max="25" width="16.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="15.6">
+    <row r="1" spans="1:25" s="4" customFormat="1" ht="15.6">
       <c r="A1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -671,145 +699,161 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" customWidth="1"/>
-    <col min="2" max="2" width="20.21875" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.33203125" customWidth="1"/>
-    <col min="8" max="8" width="25.5546875" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="14.21875" customWidth="1"/>
-    <col min="13" max="13" width="16.44140625" customWidth="1"/>
-    <col min="14" max="14" width="19.44140625" customWidth="1"/>
-    <col min="15" max="15" width="16.44140625" customWidth="1"/>
-    <col min="16" max="17" width="20.109375" customWidth="1"/>
-    <col min="18" max="18" width="22.21875" customWidth="1"/>
-    <col min="19" max="19" width="21.44140625" customWidth="1"/>
-    <col min="20" max="20" width="17.77734375" customWidth="1"/>
-    <col min="21" max="21" width="18.44140625" customWidth="1"/>
-    <col min="22" max="22" width="15.109375" customWidth="1"/>
-    <col min="23" max="23" width="16.6640625" customWidth="1"/>
-    <col min="24" max="24" width="23.77734375" customWidth="1"/>
-    <col min="25" max="25" width="19" customWidth="1"/>
-    <col min="26" max="26" width="14.21875" customWidth="1"/>
-    <col min="27" max="27" width="16.5546875" customWidth="1"/>
-    <col min="28" max="28" width="16" customWidth="1"/>
-    <col min="29" max="29" width="24.5546875" customWidth="1"/>
-    <col min="30" max="30" width="16.109375" customWidth="1"/>
-    <col min="31" max="31" width="17.109375" customWidth="1"/>
-    <col min="32" max="32" width="16.77734375" customWidth="1"/>
-    <col min="33" max="33" width="16.6640625" customWidth="1"/>
-    <col min="34" max="34" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="21.21875" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" customWidth="1"/>
+    <col min="4" max="4" width="31.21875" customWidth="1"/>
+    <col min="5" max="5" width="25.6640625" customWidth="1"/>
+    <col min="6" max="6" width="20.21875" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" customWidth="1"/>
+    <col min="9" max="9" width="20.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="35.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="21.33203125" customWidth="1"/>
+    <col min="12" max="12" width="25.5546875" customWidth="1"/>
+    <col min="13" max="13" width="19" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="16.21875" customWidth="1"/>
+    <col min="16" max="16" width="14.21875" customWidth="1"/>
+    <col min="17" max="17" width="16.44140625" customWidth="1"/>
+    <col min="18" max="18" width="19.44140625" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" customWidth="1"/>
+    <col min="20" max="21" width="20.109375" customWidth="1"/>
+    <col min="22" max="22" width="22.21875" customWidth="1"/>
+    <col min="23" max="23" width="21.44140625" customWidth="1"/>
+    <col min="24" max="24" width="17.77734375" customWidth="1"/>
+    <col min="25" max="25" width="18.44140625" customWidth="1"/>
+    <col min="26" max="26" width="15.109375" customWidth="1"/>
+    <col min="27" max="27" width="16.6640625" customWidth="1"/>
+    <col min="28" max="28" width="23.77734375" customWidth="1"/>
+    <col min="29" max="29" width="19" customWidth="1"/>
+    <col min="30" max="30" width="14.21875" customWidth="1"/>
+    <col min="31" max="31" width="16.5546875" customWidth="1"/>
+    <col min="32" max="32" width="16" customWidth="1"/>
+    <col min="33" max="33" width="24.5546875" customWidth="1"/>
+    <col min="34" max="34" width="16.109375" customWidth="1"/>
+    <col min="35" max="35" width="17.109375" customWidth="1"/>
+    <col min="36" max="36" width="16.77734375" customWidth="1"/>
+    <col min="37" max="37" width="16.6640625" customWidth="1"/>
+    <col min="38" max="38" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15.6">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:38" ht="15.6">
+      <c r="A1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>31</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>0</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>32</v>
       </c>
-      <c r="M1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="N1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="P1" t="s">
+      <c r="T1" t="s">
         <v>40</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="U1" t="s">
         <v>3</v>
       </c>
-      <c r="R1" t="s">
+      <c r="V1" t="s">
         <v>33</v>
       </c>
-      <c r="S1" t="s">
+      <c r="W1" t="s">
         <v>34</v>
       </c>
-      <c r="T1" t="s">
+      <c r="X1" t="s">
         <v>35</v>
       </c>
-      <c r="U1" t="s">
+      <c r="Y1" t="s">
         <v>1</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Z1" t="s">
         <v>2</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AA1" t="s">
         <v>41</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AB1" t="s">
         <v>42</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>45</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AD1" t="s">
         <v>43</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AE1" t="s">
         <v>44</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AF1" t="s">
         <v>19</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AG1" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AH1" t="s">
         <v>5</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AI1" t="s">
         <v>20</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AJ1" t="s">
         <v>49</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AK1" t="s">
         <v>21</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AL1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -821,88 +865,104 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" customWidth="1"/>
-    <col min="7" max="7" width="30.109375" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" customWidth="1"/>
-    <col min="10" max="10" width="25.88671875" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="22.88671875" customWidth="1"/>
-    <col min="14" max="15" width="17.6640625" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" customWidth="1"/>
-    <col min="17" max="17" width="18.88671875" customWidth="1"/>
-    <col min="18" max="18" width="19.44140625" customWidth="1"/>
-    <col min="19" max="19" width="19.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="4" max="4" width="30.21875" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" customWidth="1"/>
+    <col min="11" max="11" width="30.109375" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" customWidth="1"/>
+    <col min="13" max="13" width="20.33203125" customWidth="1"/>
+    <col min="14" max="14" width="25.88671875" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14.44140625" customWidth="1"/>
+    <col min="17" max="17" width="22.88671875" customWidth="1"/>
+    <col min="18" max="19" width="17.6640625" customWidth="1"/>
+    <col min="20" max="20" width="13.5546875" customWidth="1"/>
+    <col min="21" max="21" width="18.88671875" customWidth="1"/>
+    <col min="22" max="22" width="19.44140625" customWidth="1"/>
+    <col min="23" max="23" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.6">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:24" ht="15.6">
+      <c r="A1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>44</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (4)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (5)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A38543-519E-4CE6-A04E-4186142C4D71}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2561082B-20DC-4B0B-85DC-4AE4A12D6DE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="人工申请" sheetId="1" r:id="rId1"/>
@@ -201,23 +201,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF172B4D"/>
-      <name val="宋体"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
     </font>
     <font>
       <sz val="11"/>
@@ -233,7 +223,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -241,35 +231,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -614,80 +583,80 @@
     <col min="25" max="25" width="16.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="4" customFormat="1" ht="15.6">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:25" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="2" t="s">
         <v>38</v>
       </c>
     </row>
@@ -741,20 +710,20 @@
     <col min="38" max="38" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="15.6">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:38" ht="15">
+      <c r="A1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -775,85 +744,85 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>46</v>
       </c>
     </row>
@@ -892,77 +861,77 @@
     <col min="23" max="23" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.6">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:24" ht="15">
+      <c r="A1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="2" t="s">
         <v>44</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (5)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2561082B-20DC-4B0B-85DC-4AE4A12D6DE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44564E75-CEBA-4C8E-815D-ACFDFC15A98C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="55">
   <si>
     <t>备注</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>合同类型</t>
+  </si>
+  <si>
+    <t>修改数量备注</t>
   </si>
 </sst>
 </file>
@@ -834,7 +837,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.5546875" customWidth="1"/>
@@ -844,24 +847,25 @@
     <col min="5" max="5" width="16.6640625" customWidth="1"/>
     <col min="6" max="6" width="22.109375" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" customWidth="1"/>
-    <col min="10" max="10" width="30.6640625" customWidth="1"/>
-    <col min="11" max="11" width="30.109375" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="13" max="13" width="20.33203125" customWidth="1"/>
-    <col min="14" max="14" width="25.88671875" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" customWidth="1"/>
-    <col min="17" max="17" width="22.88671875" customWidth="1"/>
-    <col min="18" max="19" width="17.6640625" customWidth="1"/>
-    <col min="20" max="20" width="13.5546875" customWidth="1"/>
-    <col min="21" max="21" width="18.88671875" customWidth="1"/>
-    <col min="22" max="22" width="19.44140625" customWidth="1"/>
-    <col min="23" max="23" width="19.6640625" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" customWidth="1"/>
+    <col min="11" max="11" width="30.6640625" customWidth="1"/>
+    <col min="12" max="12" width="30.109375" customWidth="1"/>
+    <col min="13" max="13" width="17.6640625" customWidth="1"/>
+    <col min="14" max="14" width="20.33203125" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" customWidth="1"/>
+    <col min="17" max="17" width="14.44140625" customWidth="1"/>
+    <col min="18" max="18" width="22.88671875" customWidth="1"/>
+    <col min="19" max="20" width="17.6640625" customWidth="1"/>
+    <col min="21" max="21" width="13.5546875" customWidth="1"/>
+    <col min="22" max="22" width="18.88671875" customWidth="1"/>
+    <col min="23" max="23" width="19.44140625" customWidth="1"/>
+    <col min="24" max="24" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15">
+    <row r="1" spans="1:25" ht="15">
       <c r="A1" s="2" t="s">
         <v>50</v>
       </c>
@@ -884,54 +888,57 @@
         <v>3</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>44</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Exp_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44564E75-CEBA-4C8E-815D-ACFDFC15A98C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD63F23B-C6E4-40A9-937C-55C655901FD6}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
   <si>
     <t>备注</t>
   </si>
@@ -198,6 +198,15 @@
   </si>
   <si>
     <t>修改数量备注</t>
+  </si>
+  <si>
+    <t>归还备注</t>
+  </si>
+  <si>
+    <t>归还数量</t>
+  </si>
+  <si>
+    <t>归还时间</t>
   </si>
 </sst>
 </file>
@@ -837,7 +846,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.5546875" customWidth="1"/>
@@ -863,9 +872,14 @@
     <col min="22" max="22" width="18.88671875" customWidth="1"/>
     <col min="23" max="23" width="19.44140625" customWidth="1"/>
     <col min="24" max="24" width="19.6640625" customWidth="1"/>
+    <col min="25" max="25" width="21.109375" customWidth="1"/>
+    <col min="26" max="27" width="21.33203125" customWidth="1"/>
+    <col min="28" max="28" width="20.88671875" customWidth="1"/>
+    <col min="29" max="29" width="20.109375" customWidth="1"/>
+    <col min="30" max="30" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15">
+    <row r="1" spans="1:29" ht="15">
       <c r="A1" s="2" t="s">
         <v>50</v>
       </c>
@@ -940,6 +954,18 @@
       </c>
       <c r="Y1" s="2" t="s">
         <v>44</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
